--- a/templates/certificate_of_origin.xlsx
+++ b/templates/certificate_of_origin.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'COO'!$26:$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'COO'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'COO'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -62,11 +62,6 @@
       <name val="Arial"/>
       <sz val="12"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF595959"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -81,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,25 +98,11 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -184,10 +165,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -281,6 +258,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>19050</rowOff>
+    </from>
+    <ext cx="2333625" cy="895350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -583,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A4:F41"/>
+  <dimension ref="A4:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -607,7 +609,7 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Manufacturer's Declaration of Origin</t>
+          <t>Exporter's Declaration of Origin</t>
         </is>
       </c>
     </row>
@@ -632,12 +634,12 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Manufacturer:</t>
+          <t>Exporter:</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>NOAH Actuation Co., Ltd.</t>
+          <t>Rotork Controls Korea Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -645,27 +647,27 @@
       <c r="A11" s="3" t="n"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>11, Jeongseojin 9-ro, Seo-gu, Incheon 22850, Republic of Korea</t>
+          <t>515, 5th floor Leader’s Bldg, Jangmi-ro 42, Bundang-gu, Seongnam-si,</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Exporter:</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Rotork Controls Korea Co., Ltd.</t>
+          <t>Gyeonggi-do, 13496, Republic of Korea</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="3" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer:</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>515, 5th floor Leader’s Bldg, Jangmi-ro 42, Bundang-gu, Seongnam-si,</t>
+          <t>NOAH Actuation Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -673,7 +675,7 @@
       <c r="A14" s="3" t="n"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Gyeonggi-do, 13496, Republic of Korea</t>
+          <t>11, Jeongseojin 9-ro, Seo-gu, Incheon 22850, Republic of Korea</t>
         </is>
       </c>
     </row>
@@ -839,10 +841,10 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="80" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>NOAH Actuation Co., Ltd., as the manufacturer of the goods described above, hereby declares that the goods were manufactured in the Republic of Korea and that the information on this certificate is true and accurate. We assume the responsibility for proving such representations and understand that we shall be liable for any false statements or material omissions made on or in connection with this document. We agree to maintain, and to present upon request of the competent authority, information, documentation and necessary proof to support this certificate for a period of at least five (5) years from the date of issue, and to inform such authority in writing of any changes that could affect the accuracy or validity of this certificate.</t>
+          <t>Rotork Controls Korea Co., Ltd., as the exporter of the goods described above, hereby declares that the goods were manufactured by NOAH Actuation Co., Ltd. in the Republic of Korea and that the information on this certificate is true and accurate. We assume the responsibility for proving such representations and understand that we shall be liable for any false statements or material omissions made on or in connection with this document. We agree to maintain and to present upon request of the competent authority information, documentation and necessary proof to support this certificate and to inform such authority in writing of any changes that could affect the accuracy or validity of this certificate.</t>
         </is>
       </c>
     </row>
@@ -850,7 +852,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>For and on behalf of NOAH Actuation Co., Ltd.</t>
+          <t>For and on behalf of Rotork Controls Korea Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -862,40 +864,17 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>Incheon, Republic of Korea</t>
+          <t>Seongnam, Republic of Korea</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1"/>
     <row r="37" ht="15" customHeight="1"/>
     <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>Authorised Signature</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="23" t="n"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>Name:</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="n"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>Title:</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="n"/>
-    </row>
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="40">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C17:F17"/>
@@ -911,20 +890,17 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="B40:D40"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="B41:D41"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A23:B23"/>
@@ -944,7 +920,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 NOAH Actuation Co., Ltd.&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Rotork Controls Korea Co., Ltd.&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/templates/certificate_of_origin.xlsx
+++ b/templates/certificate_of_origin.xlsx
@@ -126,16 +126,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -588,8 +588,8 @@
   <dimension ref="A4:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -752,30 +752,30 @@
     <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Order No.</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
+          <t>Customer PO</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Model No. / Description</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>HS Code</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
@@ -784,15 +784,15 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>SOO-2026-0299</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+          <t>IK29364</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>1000057706</t>
         </is>
@@ -802,7 +802,7 @@
           <t>NA015 220/240VAC-1PH-50/60HZ ALS 90-360DEG 17STAR</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>8481.90.0000</t>
         </is>
